--- a/public/static/工具导入模板.xlsx
+++ b/public/static/工具导入模板.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="27480" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="设备档案" sheetId="1" r:id="rId1"/>
@@ -28,12 +28,19 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>序号</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工具编码(</t>
     </r>
     <r>
@@ -59,6 +66,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工具名称(</t>
     </r>
     <r>
@@ -84,6 +98,13 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>工具分类(</t>
     </r>
     <r>
@@ -109,9 +130,6 @@
   </si>
   <si>
     <t>工具规格</t>
-  </si>
-  <si>
-    <t>图号</t>
   </si>
   <si>
     <t>用途</t>
@@ -837,7 +855,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -855,9 +873,6 @@
     </xf>
     <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1395,25 +1410,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
-    <col min="1" max="1" width="7.44444444444444" style="2" customWidth="1"/>
-    <col min="2" max="2" width="18.1111111111111" style="2" customWidth="1"/>
+    <col min="1" max="1" width="7.44166666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="18.1083333333333" style="2" customWidth="1"/>
     <col min="3" max="3" width="17.3333333333333" style="2" customWidth="1"/>
-    <col min="4" max="4" width="20.4444444444444" style="2" customWidth="1"/>
+    <col min="4" max="4" width="20.4416666666667" style="2" customWidth="1"/>
     <col min="5" max="5" width="13.6666666666667" style="2" customWidth="1"/>
-    <col min="6" max="6" width="12.2222222222222" customWidth="1"/>
-    <col min="7" max="7" width="18" customWidth="1"/>
-    <col min="8" max="8" width="14.2222222222222" customWidth="1"/>
-    <col min="9" max="9" width="9.55555555555556" customWidth="1"/>
-    <col min="10" max="10" width="9.88888888888889" customWidth="1"/>
-    <col min="11" max="11" width="9.77777777777778" customWidth="1"/>
-    <col min="12" max="12" width="12.7777777777778" customWidth="1"/>
-    <col min="13" max="13" width="20.5555555555556" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14.225" customWidth="1"/>
+    <col min="8" max="8" width="9.55833333333333" customWidth="1"/>
+    <col min="9" max="9" width="9.89166666666667" customWidth="1"/>
+    <col min="10" max="10" width="9.775" customWidth="1"/>
+    <col min="11" max="11" width="12.775" customWidth="1"/>
+    <col min="12" max="12" width="20.5583333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:13">
+    <row r="1" ht="25" customHeight="1" spans="1:12">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1450,26 +1464,22 @@
       <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="4" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:12">
+      <c r="A2" s="5" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:13">
-      <c r="A2" s="5" t="s">
-        <v>13</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5"/>
       <c r="F2" s="6"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1481,29 +1491,29 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="3"/>
+  <sheetFormatPr defaultColWidth="8.89166666666667" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="82.2222222222222" customWidth="1"/>
+    <col min="1" max="1" width="82.225" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
